--- a/Assets/JJData/Xlsx/GatheringData.xlsx
+++ b/Assets/JJData/Xlsx/GatheringData.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="2"/>
@@ -523,12 +523,12 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>채집 전 스프라이트 Resources 경로</t>
+          <t>채집 전 스프라이트 이름(Atlas Key)</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>채집 후 스프라이트 Resources 경로</t>
+          <t>채집 후 스프라이트 이름(Atlas Key)</t>
         </is>
       </c>
       <c r="F1" s="6" t="inlineStr">
@@ -541,7 +541,22 @@
           <t>한 번만 채집 가능 여부</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>드랍 모드</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>설정 드랍 재료 ID A</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>설정 드랍 재료 ID B</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -583,7 +598,22 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -625,7 +655,22 @@
           <t>canGatherOnce</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>dropMode</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>configuredDropIngredientIdA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>configuredDropIngredientIdB</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>memo</t>
         </is>
@@ -645,12 +690,12 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/frozen_frog</t>
+          <t>Gathering_frozen_frog</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/frozen_frog_empty</t>
+          <t>Gathering_frozen_frog_empty</t>
         </is>
       </c>
       <c r="F4" s="8" t="n">
@@ -659,7 +704,18 @@
       <c r="G4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DataIngredient</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>지금같은 상황에 귀한 단백질원. 먹으면 혀가 길어질 것만 같은 기분이 든다. 비위가 상하지만 어쩔 수 없겠지...</t>
         </is>
@@ -679,12 +735,12 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/octopus_icicle</t>
+          <t>Gathering_octopus_icicle</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/octopus_icicle_empty</t>
+          <t>Gathering_octopus_icicle_empty</t>
         </is>
       </c>
       <c r="F5" s="8" t="n">
@@ -693,7 +749,18 @@
       <c r="G5" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DataIngredient</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>문어 빨판이 그려진 고드름. 바닥에 착하고 붙는다. 흐느적 거리는 것을 본 것 같은데... 기분 탓이겠지...</t>
         </is>
@@ -713,12 +780,12 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/frost_feather</t>
+          <t>Gathering_frost_feather</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/frost_feather_empty</t>
+          <t>Gathering_frost_feather_empty</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
@@ -727,7 +794,18 @@
       <c r="G6" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>DataIngredient</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>눈부신 빛을 뿜는 아름답고 투명한 깃털, 날개를 달아줘요!</t>
         </is>
@@ -747,12 +825,12 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/carrot_icicle</t>
+          <t>Gathering_carrot_icicle</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/carrot_icicle_empty</t>
+          <t>Gathering_carrot_icicle_empty</t>
         </is>
       </c>
       <c r="F7" s="8" t="n">
@@ -761,7 +839,18 @@
       <c r="G7" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AllConfiguredIngredients</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1201</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>1스테이지 - 당근 처럼 주황빛이 도는 고드름. 먹을 수 있을까?</t>
         </is>
@@ -781,12 +870,12 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/salty_ice</t>
+          <t>Gathering_salty_ice</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/salty_ice_empty</t>
+          <t>Gathering_salty_ice_empty</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
@@ -795,9 +884,20 @@
       <c r="G8" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>1스테이지 - 짠 맛이 난다.</t>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DataIngredient</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>1스테이지 - 짠 맛이 난다. (스테이지 강화재료 조합 채집물에 병합되어 별도 채집물로는 사용되지 않음 - 데이터 참조용)</t>
         </is>
       </c>
     </row>
@@ -815,12 +915,12 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/ice_strawberry</t>
+          <t>Gathering_ice_strawberry</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/ice_strawberry_empty</t>
+          <t>Gathering_ice_strawberry_empty</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
@@ -829,7 +929,18 @@
       <c r="G9" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AllConfiguredIngredients</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1203</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1204</v>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
         <is>
           <t>2스테이지 - 달콤한 맛이 일품! 새빨간 과즙이 팡팡! 일리가 있나... 미쳐가는군.</t>
         </is>
@@ -849,12 +960,12 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/unicorn_horn_icicle</t>
+          <t>Gathering_unicorn_horn_icicle</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/unicorn_horn_icicle_empty</t>
+          <t>Gathering_unicorn_horn_icicle_empty</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
@@ -863,9 +974,20 @@
       <c r="G10" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>2스테이지 - 소용돌이 모양 고드름이다. 마치 유니콘 뿔같군... 어린애도 아니고... 참...</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DataIngredient</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>2스테이지 - 소용돌이 모양 고드름이다. 마치 유니콘 뿔같군... 어린애도 아니고... 참... (스테이지 강화재료 조합 채집물에 병합되어 별도 채집물로는 사용되지 않음 - 데이터 참조용)</t>
         </is>
       </c>
     </row>
@@ -883,12 +1005,12 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/frozen_dinosaur_tail</t>
+          <t>Gathering_frozen_dinosaur_tail</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/frozen_dinosaur_tail_empty</t>
+          <t>Gathering_frozen_dinosaur_tail_empty</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
@@ -897,7 +1019,18 @@
       <c r="G11" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>AllConfiguredIngredients</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1205</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
         <is>
           <t>3스테이지 - 1억년전에 존재했던 지구의 지배자들의 흔적. 먹으면 힘이 불끈!</t>
         </is>
@@ -917,12 +1050,12 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/eternal_snow</t>
+          <t>Gathering_eternal_snow</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Sprites/Gatherables/eternal_snow_empty</t>
+          <t>Gathering_eternal_snow_empty</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
@@ -931,9 +1064,20 @@
       <c r="G12" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>3스테이지 - 순백색의 깨끗함의 상징. 인간의 원죄가 용서될 것 같은 맛의 전설의 눈이다.</t>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>DataIngredient</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>3스테이지 - 순백색의 깨끗함의 상징. 인간의 원죄가 용서될 것 같은 맛의 전설의 눈이다. (스테이지 강화재료 조합 채집물에 병합되어 별도 채집물로는 사용되지 않음 - 데이터 참조용)</t>
         </is>
       </c>
     </row>

--- a/Assets/JJData/Xlsx/GatheringData.xlsx
+++ b/Assets/JJData/Xlsx/GatheringData.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="2"/>
@@ -816,11 +816,11 @@
         <v>3201</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1201</v>
+        <v>0</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>당근 모양 고드름 채집물</t>
+          <t>1스테이지 강화 채집물</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -852,30 +852,30 @@
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>1스테이지 - 당근 처럼 주황빛이 도는 고드름. 먹을 수 있을까?</t>
+          <t>1스테이지 - 강화재료 두 종류(당근 모양 고드름, 짠 얼음)가 한 번에 나오는 채집물</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="8" t="n">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1202</v>
+        <v>0</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>짠 얼음 채집물</t>
+          <t>2스테이지 강화 채집물</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Gathering_salty_ice</t>
+          <t>Gathering_ice_strawberry</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Gathering_salty_ice_empty</t>
+          <t>Gathering_ice_strawberry_empty</t>
         </is>
       </c>
       <c r="F8" s="8" t="n">
@@ -886,41 +886,41 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DataIngredient</t>
+          <t>AllConfiguredIngredients</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1203</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1204</v>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>1스테이지 - 짠 맛이 난다. (스테이지 강화재료 조합 채집물에 병합되어 별도 채집물로는 사용되지 않음 - 데이터 참조용)</t>
+          <t>2스테이지 - 강화재료 두 종류(얼음 딸기, 유니콘 뿔 고드름)가 한 번에 나오는 채집물</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="8" t="n">
-        <v>3203</v>
+        <v>3205</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1203</v>
+        <v>0</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>얼음 딸기 채집물</t>
+          <t>3스테이지 강화 채집물</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Gathering_ice_strawberry</t>
+          <t>Gathering_frozen_dinosaur_tail</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Gathering_ice_strawberry_empty</t>
+          <t>Gathering_frozen_dinosaur_tail_empty</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
@@ -935,152 +935,20 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="J9" t="n">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>2스테이지 - 달콤한 맛이 일품! 새빨간 과즙이 팡팡! 일리가 있나... 미쳐가는군.</t>
+          <t>3스테이지 - 강화재료 두 종류(얼어붙은 공룡꼬리, 만년설)가 한 번에 나오는 채집물</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="8" t="n">
-        <v>3204</v>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>1204</v>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>유니콘 뿔 고드름 채집물</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Gathering_unicorn_horn_icicle</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Gathering_unicorn_horn_icicle_empty</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>DataIngredient</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="8" t="inlineStr">
-        <is>
-          <t>2스테이지 - 소용돌이 모양 고드름이다. 마치 유니콘 뿔같군... 어린애도 아니고... 참... (스테이지 강화재료 조합 채집물에 병합되어 별도 채집물로는 사용되지 않음 - 데이터 참조용)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="8" t="n">
-        <v>3205</v>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>1205</v>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>얼어붙은 공룡꼬리 채집물</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Gathering_frozen_dinosaur_tail</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Gathering_frozen_dinosaur_tail_empty</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>AllConfiguredIngredients</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1205</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1206</v>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
-        <is>
-          <t>3스테이지 - 1억년전에 존재했던 지구의 지배자들의 흔적. 먹으면 힘이 불끈!</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="8" t="n">
-        <v>3206</v>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>1206</v>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>만년설 채집물</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Gathering_eternal_snow</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Gathering_eternal_snow_empty</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>DataIngredient</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>3스테이지 - 순백색의 깨끗함의 상징. 인간의 원죄가 용서될 것 같은 맛의 전설의 눈이다. (스테이지 강화재료 조합 채집물에 병합되어 별도 채집물로는 사용되지 않음 - 데이터 참조용)</t>
-        </is>
-      </c>
-    </row>
+    <row r="10" ht="48" customHeight="1"/>
+    <row r="11" ht="48" customHeight="1"/>
+    <row r="12" ht="48" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A3:H11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
